--- a/artfynd/A 6353-2026 artfynd.xlsx
+++ b/artfynd/A 6353-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83212618</v>
+        <v>1902685</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Farsbo, Ög</t>
+          <t>Ask vid Farsbo Källa (07F8e15), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521405.8036319785</v>
+        <v>521436</v>
       </c>
       <c r="R2" t="n">
-        <v>6442017.947631758</v>
+        <v>6442151</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +738,19 @@
           <t>Ulrika</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1D20C284-B7AE-4730-AF2E-CB4E390FDEB7</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>070584151 / LEP TERE / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,73 +765,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108060385</v>
+        <v>1917502</v>
       </c>
       <c r="B3" t="n">
-        <v>105400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Farsbo källa, Ulrika kyrka, Ög</t>
+          <t>Ask vid Farsbo Källa (07F8e15), Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521435</v>
+        <v>521436</v>
       </c>
       <c r="R3" t="n">
-        <v>6442152</v>
+        <v>6442151</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,17 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2000-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2000-09-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Jätteask invid Östgötaleden och Farsbo källa (ser frisk ut)</t>
+          <t>070584151 / NEP PARI / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,24 +865,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunnar Ölfvingsson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
     </row>
@@ -919,12 +890,7 @@
         <v>110361885</v>
       </c>
       <c r="B4" t="n">
-        <v>73700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521427.2762778517</v>
+        <v>521427</v>
       </c>
       <c r="R4" t="n">
-        <v>6442158.044925709</v>
+        <v>6442158</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +955,9 @@
           <t>2022-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,53 +988,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110361882</v>
+        <v>108060490</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>100100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Farsbo, Ög</t>
+          <t>Grova lövträd vid L Farsbosjön, Ulrika kyrka, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521484.7478897091</v>
+        <v>521314</v>
       </c>
       <c r="R5" t="n">
-        <v>6442197.443483176</v>
+        <v>6442048</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>minst 2 ex hörda och sedda vid L Farsbosjön</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,12 +1090,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Gunnar Ölfvingsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Gunnar Ölfvingsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1148,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119553786</v>
+        <v>83212618</v>
       </c>
       <c r="B6" t="n">
-        <v>105564</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,23 +1139,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öst om kärret NV om Lilla Farsbo. 40 m S om stora vägen., Ög</t>
+          <t>Lilla Farsbo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521430</v>
+        <v>521406</v>
       </c>
       <c r="R6" t="n">
-        <v>6442147</v>
+        <v>6442018</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,19 +1173,19 @@
           <t>Ulrika</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1D20C284-B7AE-4730-AF2E-CB4E390FDEB7</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2001-03-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4,1 m i omkrets. Omkring 0,5 meter från marken finns det en Svavelticka (Laetiporus sulphureus) på stammen.</t>
+          <t>2001-03-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,27 +1194,463 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108060385</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Farsbo källa, Ulrika kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>521435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6442152</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Jätteask invid Östgötaleden och Farsbo källa (ser frisk ut)</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119553786</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öst om kärret NV om Lilla Farsbo. 40 m S om stora vägen., Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>521430</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6442147</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4,1 m i omkrets. Omkring 0,5 meter från marken finns det en Svavelticka (Laetiporus sulphureus) på stammen.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Simon Eneland</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Simon Eneland</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110361882</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Farsbo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>521485</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6442198</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108060460</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grova lövträd vid L Farsbosjön, Ulrika kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>521314</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6442048</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ulrika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>utbredda bålar på lutande lind i brant ned mot restaurerad betesmark</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gunnar Ölfvingsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6353-2026 artfynd.xlsx
+++ b/artfynd/A 6353-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1902685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1917502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361885</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108060490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83212618</t>
         </is>
       </c>
     </row>
@@ -1324,6 +1354,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108060385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119553786</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110361882</t>
         </is>
       </c>
     </row>
@@ -1651,8 +1696,24 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108060460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>